--- a/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:41:08+00:00</t>
+    <t>2026-08-06T10:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:59:58+00:00</t>
+    <t>2026-08-06T13:20:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:20:50+00:00</t>
+    <t>2026-08-06T13:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
+++ b/branches/migration/mii-kds-module-template/ValueSet-2.16.840.1.113883.3.1937.777.24.11.30--20210323234509.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:27:29+00:00</t>
+    <t>2026-08-06T13:31:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
